--- a/inventory/files/2026-W40/STA_US_PRIS_2026-W40.xlsx
+++ b/inventory/files/2026-W40/STA_US_PRIS_2026-W40.xlsx
@@ -1536,7 +1536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="17"/>
   <cols>
     <col width="26.5" customWidth="1" style="28" min="1" max="1"/>
@@ -1688,431 +1688,281 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PSS-11248A</t>
+          <t>USS-2603A</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>449</v>
+        <v>396</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>USS-2603A</t>
+          <t>PPS-2974A</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>368</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PPS-2974A</t>
+          <t>PSS-11248A</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>332</v>
+        <v>339</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PSS-5690A</t>
+          <t>PSS-1738A</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>228</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PSS-1738A</t>
+          <t>PSS-5690A</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>157</v>
+        <v>151</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PMB-4124A</t>
+          <t>PSS-1168A</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>98</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PSS-11181A</t>
+          <t>USS-10926A</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>82</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PSS-1168A</t>
+          <t>PMB-4124A</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>USS-10926A</t>
+          <t>UMS-10671A</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PMB-10902</t>
+          <t>PSB-4629A</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ESS-4441</t>
+          <t>UPS-2502A</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>63</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UMS-10671A</t>
+          <t>USS-1522A</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>UPS-1506A</t>
+          <t>PSS-11181A</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PSB-4629A</t>
+          <t>PSS-1610</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PSS-0106</t>
+          <t>UPS-1506A</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>UPS-2502A</t>
+          <t>PSS-0892</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PSS-1610</t>
+          <t>PSS-0118</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PPB-2794</t>
+          <t>ESS-11151A</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PMS-6964</t>
+          <t>PPS-4442A</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PSS-0892</t>
+          <t>PMB-6889</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PSS-1221</t>
+          <t>RAL-7035</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PSB-2825</t>
+          <t>PMB-10673</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PPS-4442A</t>
+          <t>PMB-6905A</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ESS-11151A</t>
+          <t>PSS-1523</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PWS-2762</t>
+          <t>SE-200</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PMB-10673</t>
+          <t>PPB-8036</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PMB-6910</t>
+          <t>PPB-5078</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PMB-6889</t>
+          <t>PSB-10083</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>UPB-5271</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>RAL-7035</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>PSS-0118</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>PSS-3063</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>PSS-0734</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>USS-1522A</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>PPB-5078</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>PMB-6924</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>PSS-1523</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>UPB-1848</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>SE-200</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>PSB-5589</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>PPB-6647</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>PPB-6404</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>PPB-4329A</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/inventory/files/2026-W40/STA_US_PRIS_2026-W40.xlsx
+++ b/inventory/files/2026-W40/STA_US_PRIS_2026-W40.xlsx
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="10">
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="12">
@@ -1742,7 +1742,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="15">
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16">
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
